--- a/docs/qa/PupBox-Website-Test-Cases.xlsx
+++ b/docs/qa/PupBox-Website-Test-Cases.xlsx
@@ -16523,7 +16523,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>Commit a705aba (labels; retry not possible — declined orders are cancelled) (fix/launch-critical)</t>
+          <t>Commit a705aba (labels) + 38c0974 (retry: declined orders stay open) (fix/launch-critical)</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
@@ -16583,10 +16583,14 @@
           <t>TC-WEB-166</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr"/>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>Commit 858b6a8 (fix/launch-critical)</t>
+        </is>
+      </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -17003,10 +17007,14 @@
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr"/>
-      <c r="K30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>Commit 38c0974 (fix/launch-critical) — verify with Flitt sandbox once keys exist (D-25)</t>
+        </is>
+      </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
